--- a/StructureDefinition-BundleInicio2.xlsx
+++ b/StructureDefinition-BundleInicio2.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
